--- a/Static Corn Template.xlsx
+++ b/Static Corn Template.xlsx
@@ -122,7 +122,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="2"/>
@@ -140,6 +140,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -545,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT10"/>
+  <dimension ref="A1:CU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="2.59765625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1138,6 +1141,11 @@
           <t>Images</t>
         </is>
       </c>
+      <c r="CU1" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
